--- a/raval-template.xlsx
+++ b/raval-template.xlsx
@@ -176,7 +176,7 @@
     <t>جدول فشرده، راست‌به‌چپ و خط‌کشی‌شده است؛ سرستون‌ها هنگام حرکت ثابت می‌مانند.</t>
   </si>
   <si>
-    <t>هر ردیف یک روز شمسی است؛ دقیقه‌های هر بخش را در خانه‌های کوچک زیر گروه بنویس. خانهٔ * یعنی هنوز زمان آن بخش تعیین نشده است.</t>
+    <t>هر ردیف یک روز شمسی است؛ دقیقه‌های هر بخش را در خانه‌های کوچک زیر گروه بنویس. خانهٔ خالی یا * یعنی فرصت ارفاقی برای جبران همان فعالیت؛ نه تعطیلی کل روز.</t>
   </si>
   <si>
     <t>جمع هر گروه و ساعت مفید روز با فرمول محاسبه می‌شود؛ خانه‌های تیره را ویرایش نکن.</t>

--- a/raval-template.xlsx
+++ b/raval-template.xlsx
@@ -74,7 +74,7 @@
     <t>فروردین</t>
   </si>
   <si>
-    <t>07:00</t>
+    <t/>
   </si>
   <si>
     <t>خیر</t>
